--- a/data/seminars.xlsx
+++ b/data/seminars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schaej17\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F4BD528-AC13-4C87-80F5-E8A338E6FD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EFD814-663F-4634-86AA-27363457E57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4561,7 +4561,7 @@
     <t>Talk_2_3_BBS Alan Bourke Gait in MS presented 20260827.pdf</t>
   </si>
   <si>
-    <t>Talk_2_4_Biomarker Society_Jannis_Mueller.pdf</t>
+    <t>Biomarker Society.pdf</t>
   </si>
 </sst>
 </file>
@@ -5333,7 +5333,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" ref="A2:A9" si="0">"27.08.2026"</f>
         <v>27.08.2026</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -5361,7 +5361,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -5389,7 +5389,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -5417,7 +5417,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -5445,7 +5445,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -5473,7 +5473,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -5501,7 +5501,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -5529,7 +5529,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="str">
-        <f>"27.08.2026"</f>
+        <f t="shared" si="0"/>
         <v>27.08.2026</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -5623,7 +5623,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
-        <f t="shared" ref="A13:A18" si="0">"30.10.2025"</f>
+        <f t="shared" ref="A13:A18" si="1">"30.10.2025"</f>
         <v>30.10.2025</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.10.2025</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -5679,7 +5679,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.10.2025</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.10.2025</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -5735,7 +5735,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.10.2025</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -5763,7 +5763,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>30.10.2025</v>
       </c>
       <c r="B18" s="32" t="s">
@@ -6045,7 +6045,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="str">
-        <f t="shared" ref="A28:A29" si="1">"19.03.2025"</f>
+        <f t="shared" ref="A28:A29" si="2">"19.03.2025"</f>
         <v>19.03.2025</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -6073,7 +6073,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>19.03.2025</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -6149,7 +6149,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="5" t="str">
-        <f t="shared" ref="A32:A40" si="2">"25.09.2024"</f>
+        <f t="shared" ref="A32:A40" si="3">"25.09.2024"</f>
         <v>25.09.2024</v>
       </c>
       <c r="B32" s="3" t="s">
@@ -6181,7 +6181,7 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B33" s="3" t="s">
@@ -6209,7 +6209,7 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -6237,7 +6237,7 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B35" s="3" t="s">
@@ -6265,7 +6265,7 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B36" s="3" t="s">
@@ -6293,7 +6293,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B37" s="3" t="s">
@@ -6321,7 +6321,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B38" s="3" t="s">
@@ -6349,7 +6349,7 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B39" s="3" t="s">
@@ -6377,7 +6377,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>25.09.2024</v>
       </c>
       <c r="B40" s="3" t="s">
@@ -6423,7 +6423,7 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="str">
-        <f t="shared" ref="A42:A48" si="3">"29.08.2024"</f>
+        <f t="shared" ref="A42:A48" si="4">"29.08.2024"</f>
         <v>29.08.2024</v>
       </c>
       <c r="B42" s="3" t="s">
@@ -6455,7 +6455,7 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B43" s="3" t="s">
@@ -6483,7 +6483,7 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B44" s="3" t="s">
@@ -6511,7 +6511,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B45" s="3" t="s">
@@ -6539,7 +6539,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B46" s="3" t="s">
@@ -6567,7 +6567,7 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B47" s="3" t="s">
@@ -6595,7 +6595,7 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>29.08.2024</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -6623,7 +6623,7 @@
     </row>
     <row r="49" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="str">
-        <f t="shared" ref="A49:A54" si="4">"16.05.2024"</f>
+        <f t="shared" ref="A49:A54" si="5">"16.05.2024"</f>
         <v>16.05.2024</v>
       </c>
       <c r="B49" s="3" t="s">
@@ -6651,7 +6651,7 @@
     </row>
     <row r="50" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05.2024</v>
       </c>
       <c r="B50" s="3" t="s">
@@ -6679,7 +6679,7 @@
     </row>
     <row r="51" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05.2024</v>
       </c>
       <c r="B51" s="3" t="s">
@@ -6707,7 +6707,7 @@
     </row>
     <row r="52" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05.2024</v>
       </c>
       <c r="B52" s="3" t="s">
@@ -6735,7 +6735,7 @@
     </row>
     <row r="53" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05.2024</v>
       </c>
       <c r="B53" s="3" t="s">
@@ -6763,7 +6763,7 @@
     </row>
     <row r="54" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16.05.2024</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -6791,7 +6791,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="str">
-        <f t="shared" ref="A55:A59" si="5">"16.05.2024"</f>
+        <f t="shared" ref="A55:A59" si="6">"16.05.2024"</f>
         <v>16.05.2024</v>
       </c>
       <c r="B55" s="3" t="s">
@@ -6819,7 +6819,7 @@
     </row>
     <row r="56" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16.05.2024</v>
       </c>
       <c r="B56" s="3" t="s">
@@ -6848,7 +6848,7 @@
     </row>
     <row r="57" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16.05.2024</v>
       </c>
       <c r="B57" s="3" t="s">
@@ -6876,7 +6876,7 @@
     </row>
     <row r="58" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16.05.2024</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -6904,7 +6904,7 @@
     </row>
     <row r="59" spans="1:12" ht="18" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>16.05.2024</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -7140,7 +7140,7 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="str">
-        <f t="shared" ref="A68:A75" si="6">"06.11.2023"</f>
+        <f t="shared" ref="A68:A75" si="7">"06.11.2023"</f>
         <v>06.11.2023</v>
       </c>
       <c r="B68" s="3" t="s">
@@ -7172,7 +7172,7 @@
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B69" s="3" t="s">
@@ -7200,7 +7200,7 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -7228,7 +7228,7 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -7256,7 +7256,7 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B72" s="3" t="s">
@@ -7284,7 +7284,7 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B73" s="3" t="s">
@@ -7312,7 +7312,7 @@
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B74" s="3" t="s">
@@ -7340,7 +7340,7 @@
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>06.11.2023</v>
       </c>
       <c r="B75" s="3" t="s">
@@ -7366,7 +7366,7 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="str">
-        <f t="shared" ref="A76:A82" si="7">"16.10.2023"</f>
+        <f t="shared" ref="A76:A82" si="8">"16.10.2023"</f>
         <v>16.10.2023</v>
       </c>
       <c r="B76" s="3" t="s">
@@ -7394,7 +7394,7 @@
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B77" s="3" t="s">
@@ -7422,7 +7422,7 @@
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B78" s="3" t="s">
@@ -7450,7 +7450,7 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B79" s="3" t="s">
@@ -7478,7 +7478,7 @@
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B80" s="3" t="s">
@@ -7506,7 +7506,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B81" s="3" t="s">
@@ -7534,7 +7534,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.10.2023</v>
       </c>
       <c r="B82" s="3" t="s">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="str">
-        <f t="shared" ref="A83:A88" si="8">"04.10.2023"</f>
+        <f t="shared" ref="A83:A88" si="9">"04.10.2023"</f>
         <v>04.10.2023</v>
       </c>
       <c r="B83" s="3" t="s">
@@ -7590,7 +7590,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>04.10.2023</v>
       </c>
       <c r="B84" s="3" t="s">
@@ -7618,7 +7618,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>04.10.2023</v>
       </c>
       <c r="B85" s="3" t="s">
@@ -7646,7 +7646,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>04.10.2023</v>
       </c>
       <c r="B86" s="3" t="s">
@@ -7674,7 +7674,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>04.10.2023</v>
       </c>
       <c r="B87" s="3" t="s">
@@ -7702,7 +7702,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>04.10.2023</v>
       </c>
       <c r="B88" s="3" t="s">
@@ -7776,7 +7776,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="str">
-        <f t="shared" ref="A91:A95" si="9">"21.06.2023"</f>
+        <f t="shared" ref="A91:A95" si="10">"21.06.2023"</f>
         <v>21.06.2023</v>
       </c>
       <c r="B91" s="3" t="s">
@@ -7804,7 +7804,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.06.2023</v>
       </c>
       <c r="B92" s="3" t="s">
@@ -7832,7 +7832,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.06.2023</v>
       </c>
       <c r="B93" s="3" t="s">
@@ -7860,7 +7860,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.06.2023</v>
       </c>
       <c r="B94" s="3" t="s">
@@ -7888,7 +7888,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>21.06.2023</v>
       </c>
       <c r="B95" s="3" t="s">
@@ -8048,7 +8048,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="str">
-        <f t="shared" ref="A101:A107" si="10">"15.03.2023"</f>
+        <f t="shared" ref="A101:A107" si="11">"15.03.2023"</f>
         <v>15.03.2023</v>
       </c>
       <c r="B101" s="3" t="s">
@@ -8078,7 +8078,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B102" s="3" t="s">
@@ -8106,7 +8106,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B103" s="3" t="s">
@@ -8134,7 +8134,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B104" s="3" t="s">
@@ -8162,7 +8162,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B105" s="3" t="s">
@@ -8190,7 +8190,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B106" s="3" t="s">
@@ -8218,7 +8218,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>15.03.2023</v>
       </c>
       <c r="B107" s="3" t="s">
@@ -8278,7 +8278,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="5" t="str">
-        <f t="shared" ref="A109:A114" si="11">"15.12.2022"</f>
+        <f t="shared" ref="A109:A114" si="12">"15.12.2022"</f>
         <v>15.12.2022</v>
       </c>
       <c r="B109" s="3" t="s">
@@ -8306,7 +8306,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.12.2022</v>
       </c>
       <c r="B110" s="3" t="s">
@@ -8334,7 +8334,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.12.2022</v>
       </c>
       <c r="B111" s="3" t="s">
@@ -8362,7 +8362,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.12.2022</v>
       </c>
       <c r="B112" s="3" t="s">
@@ -8390,7 +8390,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.12.2022</v>
       </c>
       <c r="B113" s="3" t="s">
@@ -8418,7 +8418,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="5" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>15.12.2022</v>
       </c>
       <c r="B114" s="3" t="s">
@@ -8444,7 +8444,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="5" t="str">
-        <f t="shared" ref="A115:A120" si="12">"08.12.2022"</f>
+        <f t="shared" ref="A115:A120" si="13">"08.12.2022"</f>
         <v>08.12.2022</v>
       </c>
       <c r="B115" s="3" t="s">
@@ -8476,7 +8476,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>08.12.2022</v>
       </c>
       <c r="B116" s="3" t="s">
@@ -8504,7 +8504,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>08.12.2022</v>
       </c>
       <c r="B117" s="3" t="s">
@@ -8532,7 +8532,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>08.12.2022</v>
       </c>
       <c r="B118" s="3" t="s">
@@ -8561,7 +8561,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>08.12.2022</v>
       </c>
       <c r="B119" s="3" t="s">
@@ -8589,7 +8589,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="5" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>08.12.2022</v>
       </c>
       <c r="B120" s="3" t="s">
@@ -8671,7 +8671,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="5" t="str">
-        <f t="shared" ref="A123:A125" si="13">"30.11.2022"</f>
+        <f t="shared" ref="A123:A125" si="14">"30.11.2022"</f>
         <v>30.11.2022</v>
       </c>
       <c r="B123" s="3" t="s">
@@ -8697,7 +8697,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="5" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30.11.2022</v>
       </c>
       <c r="B124" s="3" t="s">
@@ -8723,7 +8723,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="5" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>30.11.2022</v>
       </c>
       <c r="B125" s="3" t="s">
@@ -8749,7 +8749,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="17" t="str">
-        <f t="shared" ref="A126:A131" si="14">"15.07.2022"</f>
+        <f t="shared" ref="A126:A131" si="15">"15.07.2022"</f>
         <v>15.07.2022</v>
       </c>
       <c r="B126" s="14" t="s">
@@ -8779,7 +8779,7 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.07.2022</v>
       </c>
       <c r="B127" s="14" t="s">
@@ -8807,7 +8807,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.07.2022</v>
       </c>
       <c r="B128" s="14" t="s">
@@ -8835,7 +8835,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.07.2022</v>
       </c>
       <c r="B129" s="14" t="s">
@@ -8863,7 +8863,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.07.2022</v>
       </c>
       <c r="B130" s="14" t="s">
@@ -8891,7 +8891,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" s="17" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>15.07.2022</v>
       </c>
       <c r="B131" s="14" t="s">
@@ -8943,7 +8943,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="17" t="str">
-        <f t="shared" ref="A133:A139" si="15">"23.06.2022"</f>
+        <f t="shared" ref="A133:A139" si="16">"23.06.2022"</f>
         <v>23.06.2022</v>
       </c>
       <c r="B133" s="3" t="s">
@@ -8969,7 +8969,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B134" s="3" t="s">
@@ -8997,7 +8997,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B135" s="3" t="s">
@@ -9025,7 +9025,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B136" s="3" t="s">
@@ -9053,7 +9053,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B137" s="3" t="s">
@@ -9081,7 +9081,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B138" s="3" t="s">
@@ -9109,7 +9109,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="17" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23.06.2022</v>
       </c>
       <c r="B139" s="3" t="s">
@@ -9275,7 +9275,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" s="5" t="str">
-        <f t="shared" ref="A145:A147" si="16">"21.02.2022"</f>
+        <f t="shared" ref="A145:A147" si="17">"21.02.2022"</f>
         <v>21.02.2022</v>
       </c>
       <c r="B145" s="3"/>
@@ -9301,7 +9301,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" s="5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21.02.2022</v>
       </c>
       <c r="B146" s="3"/>
@@ -9327,7 +9327,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" s="5" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>21.02.2022</v>
       </c>
       <c r="B147" s="3"/>
@@ -9381,7 +9381,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" s="9" t="str">
-        <f t="shared" ref="A149:A152" si="17">"27.07.2021"</f>
+        <f t="shared" ref="A149:A152" si="18">"27.07.2021"</f>
         <v>27.07.2021</v>
       </c>
       <c r="B149" s="12"/>
@@ -9407,7 +9407,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27.07.2021</v>
       </c>
       <c r="B150" s="12"/>
@@ -9433,7 +9433,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27.07.2021</v>
       </c>
       <c r="B151" s="12"/>
@@ -9459,7 +9459,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" s="9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>27.07.2021</v>
       </c>
       <c r="B152" s="12"/>
@@ -9515,7 +9515,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" s="9" t="str">
-        <f t="shared" ref="A154:A160" si="18">"28.06.2021"</f>
+        <f t="shared" ref="A154:A160" si="19">"28.06.2021"</f>
         <v>28.06.2021</v>
       </c>
       <c r="B154" s="12"/>
@@ -9541,7 +9541,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B155" s="12"/>
@@ -9567,7 +9567,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B156" s="12"/>
@@ -9593,7 +9593,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B157" s="12"/>
@@ -9619,7 +9619,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B158" s="12"/>
@@ -9645,7 +9645,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B159" s="12"/>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" s="9" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>28.06.2021</v>
       </c>
       <c r="B160" s="12"/>
@@ -9727,7 +9727,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" s="9" t="str">
-        <f t="shared" ref="A162:A164" si="19">"16.06.2021"</f>
+        <f t="shared" ref="A162:A164" si="20">"16.06.2021"</f>
         <v>16.06.2021</v>
       </c>
       <c r="B162" s="12"/>
@@ -9753,7 +9753,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" s="9" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.06.2021</v>
       </c>
       <c r="B163" s="12"/>
@@ -9779,7 +9779,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" s="9" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.06.2021</v>
       </c>
       <c r="B164" s="12"/>
@@ -9835,7 +9835,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" s="9" t="str">
-        <f t="shared" ref="A166:A174" si="20">"22.03.2021"</f>
+        <f t="shared" ref="A166:A174" si="21">"22.03.2021"</f>
         <v>22.03.2021</v>
       </c>
       <c r="B166" s="12"/>
@@ -9861,7 +9861,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B167" s="12"/>
@@ -9887,7 +9887,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B168" s="12"/>
@@ -9913,7 +9913,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B169" s="12"/>
@@ -9939,7 +9939,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B170" s="12"/>
@@ -9965,7 +9965,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B171" s="12"/>
@@ -9991,7 +9991,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B172" s="12"/>
@@ -10017,7 +10017,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B173" s="12"/>
@@ -10043,7 +10043,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" s="9" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>22.03.2021</v>
       </c>
       <c r="B174" s="12"/>
@@ -10097,7 +10097,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" s="9" t="str">
-        <f t="shared" ref="A176:A181" si="21">"08.03.2021"</f>
+        <f t="shared" ref="A176:A181" si="22">"08.03.2021"</f>
         <v>08.03.2021</v>
       </c>
       <c r="B176" s="12"/>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>08.03.2021</v>
       </c>
       <c r="B177" s="12"/>
@@ -10149,7 +10149,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>08.03.2021</v>
       </c>
       <c r="B178" s="12"/>
@@ -10175,7 +10175,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>08.03.2021</v>
       </c>
       <c r="B179" s="12"/>
@@ -10201,7 +10201,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>08.03.2021</v>
       </c>
       <c r="B180" s="12"/>
@@ -10227,7 +10227,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" s="9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>08.03.2021</v>
       </c>
       <c r="B181" s="12"/>
@@ -10281,7 +10281,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" s="9" t="str">
-        <f t="shared" ref="A183:A189" si="22">"03.11.2020"</f>
+        <f t="shared" ref="A183:A189" si="23">"03.11.2020"</f>
         <v>03.11.2020</v>
       </c>
       <c r="B183" s="12"/>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B184" s="12"/>
@@ -10333,7 +10333,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B185" s="12"/>
@@ -10359,7 +10359,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B186" s="12"/>
@@ -10385,7 +10385,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B187" s="12"/>
@@ -10411,7 +10411,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B188" s="12"/>
@@ -10437,7 +10437,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" s="9" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>03.11.2020</v>
       </c>
       <c r="B189" s="12"/>
@@ -10493,7 +10493,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" s="9" t="str">
-        <f t="shared" ref="A191:A199" si="23">"07.09.2020"</f>
+        <f t="shared" ref="A191:A199" si="24">"07.09.2020"</f>
         <v>07.09.2020</v>
       </c>
       <c r="B191" s="12"/>
@@ -10519,7 +10519,7 @@
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B192" s="12"/>
@@ -10545,7 +10545,7 @@
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B193" s="12"/>
@@ -10571,7 +10571,7 @@
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B194" s="12"/>
@@ -10597,7 +10597,7 @@
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B195" s="12"/>
@@ -10623,7 +10623,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B196" s="12"/>
@@ -10649,7 +10649,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B197" s="12"/>
@@ -10675,7 +10675,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B198" s="12"/>
@@ -10701,7 +10701,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" s="9" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>07.09.2020</v>
       </c>
       <c r="B199" s="12"/>
@@ -10755,7 +10755,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" s="9" t="str">
-        <f t="shared" ref="A201:A204" si="24">"30.06.2020"</f>
+        <f t="shared" ref="A201:A204" si="25">"30.06.2020"</f>
         <v>30.06.2020</v>
       </c>
       <c r="B201" s="12"/>
@@ -10781,7 +10781,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30.06.2020</v>
       </c>
       <c r="B202" s="12"/>
@@ -10807,7 +10807,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30.06.2020</v>
       </c>
       <c r="B203" s="12"/>
@@ -10833,7 +10833,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" s="9" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>30.06.2020</v>
       </c>
       <c r="B204" s="12"/>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" s="9" t="str">
-        <f t="shared" ref="A206:A211" si="25">"29.06.2020"</f>
+        <f t="shared" ref="A206:A211" si="26">"29.06.2020"</f>
         <v>29.06.2020</v>
       </c>
       <c r="B206" s="12"/>
@@ -10915,7 +10915,7 @@
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.06.2020</v>
       </c>
       <c r="B207" s="12"/>
@@ -10941,7 +10941,7 @@
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.06.2020</v>
       </c>
       <c r="B208" s="12"/>
@@ -10967,7 +10967,7 @@
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.06.2020</v>
       </c>
       <c r="B209" s="12"/>
@@ -10993,7 +10993,7 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.06.2020</v>
       </c>
       <c r="B210" s="12"/>
@@ -11019,7 +11019,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" s="9" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29.06.2020</v>
       </c>
       <c r="B211" s="12"/>
@@ -11071,7 +11071,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" s="9" t="str">
-        <f t="shared" ref="A213:A215" si="26">"03.06.2020"</f>
+        <f t="shared" ref="A213:A215" si="27">"03.06.2020"</f>
         <v>03.06.2020</v>
       </c>
       <c r="B213" s="12"/>
@@ -11097,7 +11097,7 @@
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" s="9" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>03.06.2020</v>
       </c>
       <c r="B214" s="12"/>
@@ -11123,7 +11123,7 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" s="9" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>03.06.2020</v>
       </c>
       <c r="B215" s="12"/>
@@ -11177,7 +11177,7 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" s="9" t="str">
-        <f t="shared" ref="A217:A221" si="27">"06.05.2020"</f>
+        <f t="shared" ref="A217:A221" si="28">"06.05.2020"</f>
         <v>06.05.2020</v>
       </c>
       <c r="B217" s="12"/>
@@ -11203,7 +11203,7 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>06.05.2020</v>
       </c>
       <c r="B218" s="12"/>
@@ -11229,7 +11229,7 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>06.05.2020</v>
       </c>
       <c r="B219" s="12"/>
@@ -11255,7 +11255,7 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>06.05.2020</v>
       </c>
       <c r="B220" s="12"/>
@@ -11281,7 +11281,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" s="9" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>06.05.2020</v>
       </c>
       <c r="B221" s="12"/>
@@ -11333,7 +11333,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" s="9" t="str">
-        <f t="shared" ref="A223:A227" si="28">"04.02.2020"</f>
+        <f t="shared" ref="A223:A227" si="29">"04.02.2020"</f>
         <v>04.02.2020</v>
       </c>
       <c r="B223" s="12"/>
@@ -11357,7 +11357,7 @@
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>04.02.2020</v>
       </c>
       <c r="B224" s="12"/>
@@ -11381,7 +11381,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>04.02.2020</v>
       </c>
       <c r="B225" s="12"/>
@@ -11405,7 +11405,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>04.02.2020</v>
       </c>
       <c r="B226" s="12"/>
@@ -11427,7 +11427,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="9" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>04.02.2020</v>
       </c>
       <c r="B227" s="12"/>
@@ -11477,7 +11477,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="9" t="str">
-        <f t="shared" ref="A229:A236" si="29">"01.11.2019"</f>
+        <f t="shared" ref="A229:A236" si="30">"01.11.2019"</f>
         <v>01.11.2019</v>
       </c>
       <c r="B229" s="12"/>
@@ -11501,7 +11501,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B230" s="12"/>
@@ -11525,7 +11525,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B231" s="12"/>
@@ -11549,7 +11549,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B232" s="12"/>
@@ -11573,7 +11573,7 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B233" s="12"/>
@@ -11594,7 +11594,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B234" s="12"/>
@@ -11618,7 +11618,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B235" s="12"/>
@@ -11642,7 +11642,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="9" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>01.11.2019</v>
       </c>
       <c r="B236" s="12"/>
@@ -11691,7 +11691,7 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="9" t="str">
-        <f t="shared" ref="A238:A243" si="30">"21.08.2019"</f>
+        <f t="shared" ref="A238:A243" si="31">"21.08.2019"</f>
         <v>21.08.2019</v>
       </c>
       <c r="B238" s="12"/>
@@ -11714,7 +11714,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.08.2019</v>
       </c>
       <c r="B239" s="12"/>
@@ -11734,7 +11734,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.08.2019</v>
       </c>
       <c r="B240" s="12"/>
@@ -11755,7 +11755,7 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.08.2019</v>
       </c>
       <c r="B241" s="12"/>
@@ -11776,7 +11776,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.08.2019</v>
       </c>
       <c r="B242" s="12"/>
@@ -11797,7 +11797,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" s="9" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>21.08.2019</v>
       </c>
       <c r="B243" s="12"/>
@@ -11842,7 +11842,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" s="9" t="str">
-        <f t="shared" ref="A245:A251" si="31">"04.06.2019"</f>
+        <f t="shared" ref="A245:A251" si="32">"04.06.2019"</f>
         <v>04.06.2019</v>
       </c>
       <c r="B245" s="12"/>
@@ -11865,7 +11865,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B246" s="12"/>
@@ -11888,7 +11888,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B247" s="12"/>
@@ -11911,7 +11911,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B248" s="12"/>
@@ -11934,7 +11934,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B249" s="12"/>
@@ -11957,7 +11957,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B250" s="12"/>
@@ -11980,7 +11980,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" s="9" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>04.06.2019</v>
       </c>
       <c r="B251" s="12"/>
@@ -12028,7 +12028,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" s="9" t="str">
-        <f t="shared" ref="A253:A263" si="32">"10.05.2019"</f>
+        <f t="shared" ref="A253:A263" si="33">"10.05.2019"</f>
         <v>10.05.2019</v>
       </c>
       <c r="B253" s="12"/>
@@ -12051,7 +12051,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B254" s="12"/>
@@ -12074,7 +12074,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B255" s="12"/>
@@ -12097,7 +12097,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B256" s="12"/>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B257" s="12"/>
@@ -12143,7 +12143,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B258" s="12"/>
@@ -12166,7 +12166,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B259" s="12"/>
@@ -12189,7 +12189,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B260" s="12"/>
@@ -12212,7 +12212,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B261" s="12"/>
@@ -12235,7 +12235,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B262" s="12"/>
@@ -12255,7 +12255,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" s="9" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.05.2019</v>
       </c>
       <c r="B263" s="12"/>
@@ -12300,7 +12300,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" s="9" t="str">
-        <f t="shared" ref="A265:A272" si="33">"27.06.2018"</f>
+        <f t="shared" ref="A265:A272" si="34">"27.06.2018"</f>
         <v>27.06.2018</v>
       </c>
       <c r="B265" s="12"/>
@@ -12323,7 +12323,7 @@
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B266" s="12"/>
@@ -12346,7 +12346,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B267" s="12"/>
@@ -12369,7 +12369,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B268" s="12"/>
@@ -12392,7 +12392,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B269" s="12"/>
@@ -12415,7 +12415,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B270" s="12"/>
@@ -12438,7 +12438,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B271" s="12"/>
@@ -12461,7 +12461,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" s="9" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.06.2018</v>
       </c>
       <c r="B272" s="12"/>
@@ -12509,7 +12509,7 @@
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" s="9" t="str">
-        <f t="shared" ref="A274:A275" si="34">"26.06.2018"</f>
+        <f t="shared" ref="A274:A275" si="35">"26.06.2018"</f>
         <v>26.06.2018</v>
       </c>
       <c r="B274" s="12"/>
@@ -12532,7 +12532,7 @@
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" s="9" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>26.06.2018</v>
       </c>
       <c r="B275" s="12"/>
@@ -12580,7 +12580,7 @@
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" s="9" t="str">
-        <f t="shared" ref="A277:A280" si="35">"17.04.2018"</f>
+        <f t="shared" ref="A277:A280" si="36">"17.04.2018"</f>
         <v>17.04.2018</v>
       </c>
       <c r="B277" s="12"/>
@@ -12603,7 +12603,7 @@
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.04.2018</v>
       </c>
       <c r="B278" s="12"/>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.04.2018</v>
       </c>
       <c r="B279" s="12"/>
@@ -12649,7 +12649,7 @@
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" s="9" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.04.2018</v>
       </c>
       <c r="B280" s="12"/>
@@ -12697,7 +12697,7 @@
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" s="9" t="str">
-        <f t="shared" ref="A282:A283" si="36">"20.03.2018"</f>
+        <f t="shared" ref="A282:A283" si="37">"20.03.2018"</f>
         <v>20.03.2018</v>
       </c>
       <c r="B282" s="12"/>
@@ -12720,7 +12720,7 @@
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" s="9" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>20.03.2018</v>
       </c>
       <c r="B283" s="12"/>
@@ -12843,7 +12843,7 @@
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" s="9" t="str">
-        <f t="shared" ref="A288:A294" si="37">"11.09.2017"</f>
+        <f t="shared" ref="A288:A294" si="38">"11.09.2017"</f>
         <v>11.09.2017</v>
       </c>
       <c r="B288" s="12"/>
@@ -12867,7 +12867,7 @@
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B289" s="12"/>
@@ -12891,7 +12891,7 @@
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B290" s="12"/>
@@ -12915,7 +12915,7 @@
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B291" s="12"/>
@@ -12939,7 +12939,7 @@
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B292" s="12"/>
@@ -12963,7 +12963,7 @@
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B293" s="12"/>
@@ -12987,7 +12987,7 @@
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" s="9" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>11.09.2017</v>
       </c>
       <c r="B294" s="12"/>
@@ -13037,7 +13037,7 @@
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" s="9" t="str">
-        <f t="shared" ref="A296:A297" si="38">"26.06.2017"</f>
+        <f t="shared" ref="A296:A297" si="39">"26.06.2017"</f>
         <v>26.06.2017</v>
       </c>
       <c r="B296" s="12"/>
@@ -13061,7 +13061,7 @@
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" s="9" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>26.06.2017</v>
       </c>
       <c r="B297" s="12"/>
@@ -13085,7 +13085,7 @@
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" s="9" t="str">
-        <f t="shared" ref="A298:A306" si="39">"15.06.2017"</f>
+        <f t="shared" ref="A298:A306" si="40">"15.06.2017"</f>
         <v>15.06.2017</v>
       </c>
       <c r="B298" s="12" t="s">
@@ -13110,7 +13110,7 @@
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B299" s="12"/>
@@ -13133,7 +13133,7 @@
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B300" s="12"/>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B301" s="12"/>
@@ -13179,7 +13179,7 @@
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B302" s="12"/>
@@ -13202,7 +13202,7 @@
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B303" s="12"/>
@@ -13225,7 +13225,7 @@
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B304" s="12"/>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B305" s="12"/>
@@ -13271,7 +13271,7 @@
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" s="9" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>15.06.2017</v>
       </c>
       <c r="B306" s="12"/>
@@ -13319,7 +13319,7 @@
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" s="9" t="str">
-        <f t="shared" ref="A308:A312" si="40">"05.05.2017"</f>
+        <f t="shared" ref="A308:A312" si="41">"05.05.2017"</f>
         <v>05.05.2017</v>
       </c>
       <c r="B308" s="12"/>
@@ -13342,7 +13342,7 @@
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>05.05.2017</v>
       </c>
       <c r="B309" s="12"/>
@@ -13365,7 +13365,7 @@
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>05.05.2017</v>
       </c>
       <c r="B310" s="12"/>
@@ -13388,7 +13388,7 @@
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>05.05.2017</v>
       </c>
       <c r="B311" s="12"/>
@@ -13411,7 +13411,7 @@
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" s="9" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>05.05.2017</v>
       </c>
       <c r="B312" s="12"/>
@@ -13511,7 +13511,7 @@
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" s="9" t="str">
-        <f t="shared" ref="A316:A319" si="41">"29.11.2016"</f>
+        <f t="shared" ref="A316:A319" si="42">"29.11.2016"</f>
         <v>29.11.2016</v>
       </c>
       <c r="B316" s="12"/>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29.11.2016</v>
       </c>
       <c r="B317" s="12"/>
@@ -13557,7 +13557,7 @@
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29.11.2016</v>
       </c>
       <c r="B318" s="12"/>
@@ -13580,7 +13580,7 @@
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" s="9" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>29.11.2016</v>
       </c>
       <c r="B319" s="12"/>
@@ -13629,7 +13629,7 @@
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" s="9" t="str">
-        <f t="shared" ref="A321:A323" si="42">"14.11.2016"</f>
+        <f t="shared" ref="A321:A323" si="43">"14.11.2016"</f>
         <v>14.11.2016</v>
       </c>
       <c r="B321" s="12"/>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" s="9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14.11.2016</v>
       </c>
       <c r="B322" s="12"/>
@@ -13677,7 +13677,7 @@
     </row>
     <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" s="9" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>14.11.2016</v>
       </c>
       <c r="B323" s="12"/>
@@ -13727,7 +13727,7 @@
     </row>
     <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" s="9" t="str">
-        <f t="shared" ref="A325:A326" si="43">"17.10.2016"</f>
+        <f t="shared" ref="A325:A326" si="44">"17.10.2016"</f>
         <v>17.10.2016</v>
       </c>
       <c r="B325" s="12"/>
@@ -13751,7 +13751,7 @@
     </row>
     <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" s="9" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>17.10.2016</v>
       </c>
       <c r="B326" s="12"/>
@@ -13801,7 +13801,7 @@
     </row>
     <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" s="9" t="str">
-        <f t="shared" ref="A328:A332" si="44">"14.09.2016"</f>
+        <f t="shared" ref="A328:A332" si="45">"14.09.2016"</f>
         <v>14.09.2016</v>
       </c>
       <c r="B328" s="12"/>
@@ -13825,7 +13825,7 @@
     </row>
     <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" s="9" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.09.2016</v>
       </c>
       <c r="B329" s="12"/>
@@ -13849,7 +13849,7 @@
     </row>
     <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" s="9" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.09.2016</v>
       </c>
       <c r="B330" s="12"/>
@@ -13873,7 +13873,7 @@
     </row>
     <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" s="9" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.09.2016</v>
       </c>
       <c r="B331" s="12"/>
@@ -13897,7 +13897,7 @@
     </row>
     <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" s="9" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>14.09.2016</v>
       </c>
       <c r="B332" s="12"/>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" s="9" t="str">
-        <f t="shared" ref="A338:A346" si="45">"28.04.2016"</f>
+        <f t="shared" ref="A338:A346" si="46">"28.04.2016"</f>
         <v>28.04.2016</v>
       </c>
       <c r="B338" s="12"/>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B339" s="12"/>
@@ -14083,7 +14083,7 @@
     </row>
     <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B340" s="12"/>
@@ -14107,7 +14107,7 @@
     </row>
     <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B341" s="12"/>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B342" s="12"/>
@@ -14155,7 +14155,7 @@
     </row>
     <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B343" s="12"/>
@@ -14179,7 +14179,7 @@
     </row>
     <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B344" s="12"/>
@@ -14201,7 +14201,7 @@
     </row>
     <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B345" s="12"/>
@@ -14225,7 +14225,7 @@
     </row>
     <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>28.04.2016</v>
       </c>
       <c r="B346" s="12"/>
@@ -14273,7 +14273,7 @@
     </row>
     <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" s="9" t="str">
-        <f t="shared" ref="A348:A352" si="46">"13.01.2016"</f>
+        <f t="shared" ref="A348:A352" si="47">"13.01.2016"</f>
         <v>13.01.2016</v>
       </c>
       <c r="B348" s="12"/>
@@ -14297,7 +14297,7 @@
     </row>
     <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>13.01.2016</v>
       </c>
       <c r="B349" s="12"/>
@@ -14321,7 +14321,7 @@
     </row>
     <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>13.01.2016</v>
       </c>
       <c r="B350" s="12"/>
@@ -14345,7 +14345,7 @@
     </row>
     <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>13.01.2016</v>
       </c>
       <c r="B351" s="12"/>
@@ -14367,7 +14367,7 @@
     </row>
     <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" s="9" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>13.01.2016</v>
       </c>
       <c r="B352" s="12"/>
@@ -14465,7 +14465,7 @@
     </row>
     <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" s="9" t="str">
-        <f t="shared" ref="A356:A365" si="47">"23.06.2015"</f>
+        <f t="shared" ref="A356:A365" si="48">"23.06.2015"</f>
         <v>23.06.2015</v>
       </c>
       <c r="B356" s="12"/>
@@ -14487,7 +14487,7 @@
     </row>
     <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B357" s="12"/>
@@ -14511,7 +14511,7 @@
     </row>
     <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B358" s="12"/>
@@ -14535,7 +14535,7 @@
     </row>
     <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B359" s="12"/>
@@ -14559,7 +14559,7 @@
     </row>
     <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B360" s="12"/>
@@ -14583,7 +14583,7 @@
     </row>
     <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B361" s="12"/>
@@ -14607,7 +14607,7 @@
     </row>
     <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B362" s="12"/>
@@ -14631,7 +14631,7 @@
     </row>
     <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B363" s="12"/>
@@ -14655,7 +14655,7 @@
     </row>
     <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B364" s="12"/>
@@ -14679,7 +14679,7 @@
     </row>
     <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" s="9" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>23.06.2015</v>
       </c>
       <c r="B365" s="12"/>
@@ -14803,7 +14803,7 @@
     </row>
     <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" s="9" t="str">
-        <f t="shared" ref="A370:A376" si="48">"13.11.2014"</f>
+        <f t="shared" ref="A370:A376" si="49">"13.11.2014"</f>
         <v>13.11.2014</v>
       </c>
       <c r="B370" s="12"/>
@@ -14827,7 +14827,7 @@
     </row>
     <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B371" s="12"/>
@@ -14851,7 +14851,7 @@
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B372" s="12"/>
@@ -14875,7 +14875,7 @@
     </row>
     <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B373" s="12"/>
@@ -14899,7 +14899,7 @@
     </row>
     <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B374" s="12"/>
@@ -14923,7 +14923,7 @@
     </row>
     <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B375" s="12"/>
@@ -14947,7 +14947,7 @@
     </row>
     <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" s="9" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>13.11.2014</v>
       </c>
       <c r="B376" s="12"/>
@@ -14997,7 +14997,7 @@
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" s="9" t="str">
-        <f t="shared" ref="A378:A383" si="49">"02.10.2014"</f>
+        <f t="shared" ref="A378:A383" si="50">"02.10.2014"</f>
         <v>02.10.2014</v>
       </c>
       <c r="B378" s="12"/>
@@ -15021,7 +15021,7 @@
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" s="9" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>02.10.2014</v>
       </c>
       <c r="B379" s="12"/>
@@ -15045,7 +15045,7 @@
     </row>
     <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" s="9" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>02.10.2014</v>
       </c>
       <c r="B380" s="12"/>
@@ -15069,7 +15069,7 @@
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" s="9" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>02.10.2014</v>
       </c>
       <c r="B381" s="12"/>
@@ -15093,7 +15093,7 @@
     </row>
     <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" s="9" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>02.10.2014</v>
       </c>
       <c r="B382" s="12"/>
@@ -15117,7 +15117,7 @@
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" s="9" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>02.10.2014</v>
       </c>
       <c r="B383" s="12"/>
@@ -15305,7 +15305,7 @@
     </row>
     <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" s="9" t="str">
-        <f t="shared" ref="A391:A403" si="50">"04.06.2013"</f>
+        <f t="shared" ref="A391:A403" si="51">"04.06.2013"</f>
         <v>04.06.2013</v>
       </c>
       <c r="B391" s="12"/>
@@ -15329,7 +15329,7 @@
     </row>
     <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B392" s="12"/>
@@ -15353,7 +15353,7 @@
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B393" s="12"/>
@@ -15377,7 +15377,7 @@
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B394" s="12"/>
@@ -15401,7 +15401,7 @@
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B395" s="12"/>
@@ -15425,7 +15425,7 @@
     </row>
     <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B396" s="12"/>
@@ -15449,7 +15449,7 @@
     </row>
     <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B397" s="12"/>
@@ -15473,7 +15473,7 @@
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B398" s="12"/>
@@ -15497,7 +15497,7 @@
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B399" s="12"/>
@@ -15521,7 +15521,7 @@
     </row>
     <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B400" s="12"/>
@@ -15545,7 +15545,7 @@
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B401" s="12"/>
@@ -15569,7 +15569,7 @@
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B402" s="12"/>
@@ -15593,7 +15593,7 @@
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" s="9" t="str">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>04.06.2013</v>
       </c>
       <c r="B403" s="12"/>
@@ -15643,7 +15643,7 @@
     </row>
     <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" s="9" t="str">
-        <f t="shared" ref="A405:A406" si="51">"28.11.2012"</f>
+        <f t="shared" ref="A405:A406" si="52">"28.11.2012"</f>
         <v>28.11.2012</v>
       </c>
       <c r="B405" s="12"/>
@@ -15667,7 +15667,7 @@
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" s="9" t="str">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>28.11.2012</v>
       </c>
       <c r="B406" s="12"/>
@@ -15717,7 +15717,7 @@
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" s="9" t="str">
-        <f t="shared" ref="A408:A411" si="52">"25.09.2012"</f>
+        <f t="shared" ref="A408:A411" si="53">"25.09.2012"</f>
         <v>25.09.2012</v>
       </c>
       <c r="B408" s="12"/>
@@ -15741,7 +15741,7 @@
     </row>
     <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>25.09.2012</v>
       </c>
       <c r="B409" s="12"/>
@@ -15765,7 +15765,7 @@
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>25.09.2012</v>
       </c>
       <c r="B410" s="12"/>
@@ -15789,7 +15789,7 @@
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" s="9" t="str">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>25.09.2012</v>
       </c>
       <c r="B411" s="12"/>
@@ -15839,7 +15839,7 @@
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" s="9" t="str">
-        <f t="shared" ref="A413:A415" si="53">"09.07.2012"</f>
+        <f t="shared" ref="A413:A415" si="54">"09.07.2012"</f>
         <v>09.07.2012</v>
       </c>
       <c r="B413" s="12"/>
@@ -15863,7 +15863,7 @@
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" s="9" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>09.07.2012</v>
       </c>
       <c r="B414" s="12"/>
@@ -15885,7 +15885,7 @@
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" s="9" t="str">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>09.07.2012</v>
       </c>
       <c r="B415" s="12"/>
@@ -16005,7 +16005,7 @@
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" s="9" t="str">
-        <f t="shared" ref="A420:A426" si="54">"16.09.2011"</f>
+        <f t="shared" ref="A420:A426" si="55">"16.09.2011"</f>
         <v>16.09.2011</v>
       </c>
       <c r="B420" s="12"/>
@@ -16029,7 +16029,7 @@
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B421" s="12"/>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B422" s="12"/>
@@ -16075,7 +16075,7 @@
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B423" s="12"/>
@@ -16099,7 +16099,7 @@
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B424" s="12"/>
@@ -16123,7 +16123,7 @@
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B425" s="12"/>
@@ -16145,7 +16145,7 @@
     </row>
     <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" s="9" t="str">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>16.09.2011</v>
       </c>
       <c r="B426" s="12"/>
@@ -16195,7 +16195,7 @@
     </row>
     <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" s="9" t="str">
-        <f t="shared" ref="A428:A430" si="55">"21.07.2011"</f>
+        <f t="shared" ref="A428:A430" si="56">"21.07.2011"</f>
         <v>21.07.2011</v>
       </c>
       <c r="B428" s="12"/>
@@ -16219,7 +16219,7 @@
     </row>
     <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" s="9" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>21.07.2011</v>
       </c>
       <c r="B429" s="12"/>
@@ -16243,7 +16243,7 @@
     </row>
     <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" s="9" t="str">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>21.07.2011</v>
       </c>
       <c r="B430" s="12"/>
@@ -16293,7 +16293,7 @@
     </row>
     <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" s="9" t="str">
-        <f t="shared" ref="A432:A439" si="56">"10.05.2011"</f>
+        <f t="shared" ref="A432:A439" si="57">"10.05.2011"</f>
         <v>10.05.2011</v>
       </c>
       <c r="B432" s="12"/>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B433" s="12"/>
@@ -16341,7 +16341,7 @@
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B434" s="12"/>
@@ -16365,7 +16365,7 @@
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B435" s="12"/>
@@ -16389,7 +16389,7 @@
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B436" s="12"/>
@@ -16413,7 +16413,7 @@
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B437" s="12"/>
@@ -16437,7 +16437,7 @@
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B438" s="12"/>
@@ -16461,7 +16461,7 @@
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" s="9" t="str">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>10.05.2011</v>
       </c>
       <c r="B439" s="12"/>
@@ -16511,7 +16511,7 @@
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" s="9" t="str">
-        <f t="shared" ref="A441:A444" si="57">"07.05.2011"</f>
+        <f t="shared" ref="A441:A444" si="58">"07.05.2011"</f>
         <v>07.05.2011</v>
       </c>
       <c r="B441" s="12"/>
@@ -16535,7 +16535,7 @@
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>07.05.2011</v>
       </c>
       <c r="B442" s="12"/>
@@ -16557,7 +16557,7 @@
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>07.05.2011</v>
       </c>
       <c r="B443" s="12"/>
@@ -16581,7 +16581,7 @@
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" s="9" t="str">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>07.05.2011</v>
       </c>
       <c r="B444" s="12"/>
@@ -16726,7 +16726,7 @@
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" s="9" t="str">
-        <f t="shared" ref="A450:A459" si="58">"04.10.2010"</f>
+        <f t="shared" ref="A450:A459" si="59">"04.10.2010"</f>
         <v>04.10.2010</v>
       </c>
       <c r="B450" s="12"/>
@@ -16749,7 +16749,7 @@
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B451" s="12"/>
@@ -16772,7 +16772,7 @@
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B452" s="12"/>
@@ -16795,7 +16795,7 @@
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B453" s="12"/>
@@ -16819,7 +16819,7 @@
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B454" s="12"/>
@@ -16845,7 +16845,7 @@
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B455" s="12"/>
@@ -16871,7 +16871,7 @@
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B456" s="12"/>
@@ -16892,7 +16892,7 @@
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B457" s="12"/>
@@ -16918,7 +16918,7 @@
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B458" s="12"/>
@@ -16942,7 +16942,7 @@
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" s="9" t="str">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>04.10.2010</v>
       </c>
       <c r="B459" s="12"/>
@@ -16994,7 +16994,7 @@
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" s="9" t="str">
-        <f t="shared" ref="A461:A466" si="59">"24.06.2010"</f>
+        <f t="shared" ref="A461:A466" si="60">"24.06.2010"</f>
         <v>24.06.2010</v>
       </c>
       <c r="B461" s="12"/>
@@ -17018,7 +17018,7 @@
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" s="9" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>24.06.2010</v>
       </c>
       <c r="B462" s="12"/>
@@ -17042,7 +17042,7 @@
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" s="9" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>24.06.2010</v>
       </c>
       <c r="B463" s="12"/>
@@ -17066,7 +17066,7 @@
     </row>
     <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" s="9" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>24.06.2010</v>
       </c>
       <c r="B464" s="12"/>
@@ -17090,7 +17090,7 @@
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" s="9" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>24.06.2010</v>
       </c>
       <c r="B465" s="12"/>
@@ -17114,7 +17114,7 @@
     </row>
     <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" s="9" t="str">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>24.06.2010</v>
       </c>
       <c r="B466" s="12"/>
@@ -17216,7 +17216,7 @@
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" s="9" t="str">
-        <f t="shared" ref="A470:A475" si="60">"12.03.2010"</f>
+        <f t="shared" ref="A470:A475" si="61">"12.03.2010"</f>
         <v>12.03.2010</v>
       </c>
       <c r="B470" s="12"/>
@@ -17240,7 +17240,7 @@
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" s="9" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>12.03.2010</v>
       </c>
       <c r="B471" s="12"/>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" s="9" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>12.03.2010</v>
       </c>
       <c r="B472" s="12"/>
@@ -17288,7 +17288,7 @@
     </row>
     <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" s="9" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>12.03.2010</v>
       </c>
       <c r="B473" s="12"/>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" s="9" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>12.03.2010</v>
       </c>
       <c r="B474" s="12"/>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" s="9" t="str">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>12.03.2010</v>
       </c>
       <c r="B475" s="12"/>
